--- a/data/trans_camb/IP19C05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 0,0</t>
+          <t>-15,89; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 5,85</t>
+          <t>-9,59; 7,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 12,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,57</t>
+          <t>-2,67; 4,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 5,28</t>
+          <t>-2,61; 6,5</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 13,44</t>
+          <t>0,29; 13,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,49</t>
+          <t>-2,02; 7,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 4,57</t>
+          <t>-4,91; 4,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,68</t>
+          <t>-5,63; 2,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,11</t>
+          <t>-0,92; 6,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,13</t>
+          <t>-2,62; 3,2</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,0; 1323,2</t>
+          <t>-59,39; 1078,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 2,16</t>
+          <t>-9,07; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 7,9</t>
+          <t>-4,11; 7,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,54</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,61</t>
+          <t>-2,07; 4,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,72</t>
+          <t>-2,46; 3,71</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 19,93</t>
+          <t>-2,36; 17,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 17,8</t>
+          <t>-4,92; 17,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,39</t>
+          <t>0,0; 16,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 33,89</t>
+          <t>4,93; 35,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 13,92</t>
+          <t>0,19; 12,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 21,96</t>
+          <t>1,38; 20,9</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,65</t>
+          <t>0,0; 9,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 0,0</t>
+          <t>-4,79; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,89</t>
+          <t>-1,9; 4,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,63</t>
+          <t>-0,97; 1,62</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,96</t>
+          <t>-0,45; 4,79</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,81</t>
+          <t>-0,79; 5,93</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,74</t>
+          <t>-0,8; 5,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,78</t>
+          <t>-4,67; 1,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 3,79</t>
+          <t>-3,71; 3,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,04</t>
+          <t>-1,73; 2,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,31</t>
+          <t>-1,35; 3,4</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 745,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-80,59; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,45</t>
+          <t>0,2; 3,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,32</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,22</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,12</t>
+          <t>-0,69; 2,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,3</t>
+          <t>0,15; 2,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,27</t>
+          <t>0,05; 2,28</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 902,71</t>
+          <t>-7,26; 948,17</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 836,63</t>
+          <t>-10,95; 904,66</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 522,94</t>
+          <t>-47,01; 524,91</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-54,87; 496,75</t>
+          <t>-52,76; 479,87</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,29; 421,86</t>
+          <t>0,5; 370,74</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,03; 411,11</t>
+          <t>-11,9; 346,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 0,0</t>
+          <t>-12,79; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 7,67</t>
+          <t>-9,67; 6,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,82</t>
+          <t>0,0; 13,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 8,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,86</t>
+          <t>-2,65; 4,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 6,5</t>
+          <t>-2,49; 6,4</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 13,35</t>
+          <t>0,61; 12,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 7,41</t>
+          <t>-2,12; 6,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,39</t>
+          <t>-4,82; 4,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,66</t>
+          <t>-5,58; 3,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,5</t>
+          <t>-1,05; 6,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,2</t>
+          <t>-2,89; 2,77</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 1078,87</t>
+          <t>-60,94; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 2,05</t>
+          <t>-8,13; 2,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 7,89</t>
+          <t>-4,11; 7,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,59</t>
+          <t>0,0; 11,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,17</t>
+          <t>-1,81; 4,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,71</t>
+          <t>-2,48; 3,45</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 17,54</t>
+          <t>-2,34; 17,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 17,24</t>
+          <t>-4,91; 18,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,26</t>
+          <t>0,0; 16,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,93; 35,26</t>
+          <t>4,95; 37,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 12,91</t>
+          <t>0,14; 13,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 20,9</t>
+          <t>1,35; 22,96</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>0,0; 13,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>0,0; 7,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,64</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,0</t>
+          <t>-4,74; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,92</t>
+          <t>-1,9; 4,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,62</t>
+          <t>-0,97; 2,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,79</t>
+          <t>-0,46; 4,58</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,93</t>
+          <t>-0,79; 6,84</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,53</t>
+          <t>-0,8; 5,37</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,78</t>
+          <t>-4,76; 1,76</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,76</t>
+          <t>-3,68; 3,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,72</t>
+          <t>-1,68; 2,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,4</t>
+          <t>-1,32; 3,2</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 745,65</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,51</t>
+          <t>0,31; 3,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,05; 3,53</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,53; 2,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,13</t>
+          <t>-0,55; 2,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,31</t>
+          <t>0,17; 2,22</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,28</t>
+          <t>0,1; 2,17</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 948,17</t>
+          <t>-12,08; 812,05</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 904,66</t>
+          <t>-22,92; 717,05</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 524,91</t>
+          <t>-51,66; 594,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 479,87</t>
+          <t>-52,98; 707,1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,5; 370,74</t>
+          <t>1,89; 396,99</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 346,45</t>
+          <t>-7,59; 410,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-3,1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 0,0</t>
+          <t>0,0; 14,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 6,22</t>
+          <t>0,0; 12,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,31</t>
+          <t>-15,7; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>-9,52; 5,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,54</t>
+          <t>-2,66; 4,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,4</t>
+          <t>-2,63; 5,28</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-6,57%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>4,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1,42</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 12,67</t>
+          <t>-4,35; 4,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 6,46</t>
+          <t>-5,88; 2,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 4,57</t>
+          <t>0,19; 13,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 3,16</t>
+          <t>-2,07; 6,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 6,76</t>
+          <t>-1,56; 6,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,77</t>
+          <t>-2,84; 3,13</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-1,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-43,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>448,03%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>128,83%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,7%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-43,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,94; —</t>
+          <t>-69,0; 1323,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-1,02</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,84</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 2,15</t>
+          <t>0,0; 10,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 7,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>-8,23; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,52; 7,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,35</t>
+          <t>-2,09; 4,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,45</t>
+          <t>-2,15; 3,72</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-49,06%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>88,59%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14,94</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>5,97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,95</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14,94</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 17,92</t>
+          <t>0,0; 18,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 18,13</t>
+          <t>4,98; 33,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,39</t>
+          <t>-2,25; 19,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 37,15</t>
+          <t>-4,89; 17,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 13,56</t>
+          <t>0,12; 13,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 22,96</t>
+          <t>1,3; 21,96</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>243,62%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>79,64%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>2,07</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1,83</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>1,09</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2,6</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>-5,27; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>-1,9; 3,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 0,0</t>
+          <t>0,0; 5,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,77</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,1</t>
+          <t>-0,97; 1,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,58</t>
+          <t>-0,38; 4,96</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>1,78</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1,68</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,84</t>
+          <t>-4,63; 1,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,37</t>
+          <t>-3,61; 3,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,76</t>
+          <t>-0,8; 5,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,83</t>
+          <t>-0,8; 5,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,8</t>
+          <t>-1,63; 3,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,2</t>
+          <t>-1,33; 3,31</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-51,49%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>226,1%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>213,07%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-51,49%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,59; —</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1,55</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,54</t>
+          <t>-0,61; 2,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,53</t>
+          <t>-0,66; 2,12</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,18</t>
+          <t>0,2; 3,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,36</t>
+          <t>0,14; 3,32</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,22</t>
+          <t>0,17; 2,3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,17</t>
+          <t>0,09; 2,27</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>71,24%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>171,83%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>160,17%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>74,0%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>71,24%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 812,05</t>
+          <t>-54,01; 522,94</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 717,05</t>
+          <t>-54,87; 496,75</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 594,21</t>
+          <t>-5,47; 902,71</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 707,1</t>
+          <t>-15,93; 836,63</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,89; 396,99</t>
+          <t>5,29; 421,86</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 410,21</t>
+          <t>2,03; 411,11</t>
         </is>
       </c>
     </row>
